--- a/Experiments/20260908_wavelength_calibration.xlsx
+++ b/Experiments/20260908_wavelength_calibration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lguser\Documents\GitHub\CDspectrometer\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EF9308-EC4E-43C0-8E1C-C70234359A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F20C75-E30B-4523-924C-2D3BB8E16FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>Pixel Number (X)</t>
   </si>
@@ -89,6 +89,12 @@
   <si>
     <t>Wavelength Calibration</t>
   </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
 </sst>
 </file>
 
@@ -97,7 +103,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +147,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -203,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -218,11 +230,8 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,10 +1340,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$L$5:$L$26</c:f>
+              <c:f>'Wavelength Calibration'!$L$5:$L$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>1786</c:v>
                 </c:pt>
@@ -1403,10 +1412,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$M$5:$M$26</c:f>
+              <c:f>'Wavelength Calibration'!$M$5:$M$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>650</c:v>
                 </c:pt>
@@ -1566,10 +1575,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$L$5:$L$26</c:f>
+              <c:f>'Wavelength Calibration'!$L$5:$L$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>1786</c:v>
                 </c:pt>
@@ -1638,10 +1647,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$N$5:$N$26</c:f>
+              <c:f>'Wavelength Calibration'!$N$5:$N$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>650.03276004180066</c:v>
                 </c:pt>
@@ -1704,9 +1713,6 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>861.43537367907629</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>173.17781565715251</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2202,10 +2208,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$L$5:$L$26</c:f>
+              <c:f>'Wavelength Calibration'!$L$5:$L$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>1786</c:v>
                 </c:pt>
@@ -2274,10 +2280,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$M$5:$M$26</c:f>
+              <c:f>'Wavelength Calibration'!$M$5:$M$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>650</c:v>
                 </c:pt>
@@ -2429,10 +2435,10 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$L$5:$L$26</c:f>
+              <c:f>'Wavelength Calibration'!$L$5:$L$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>1786</c:v>
                 </c:pt>
@@ -2501,10 +2507,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'Wavelength Calibration'!$N$5:$N$26</c:f>
+              <c:f>'Wavelength Calibration'!$N$5:$N$25</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="21"/>
                 <c:pt idx="0">
                   <c:v>650.03276004180066</c:v>
                 </c:pt>
@@ -2567,9 +2573,6 @@
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>861.43537367907629</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>173.17781565715251</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2765,7 +2768,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Wavelength Calibration'!$B$5:$B$16</c15:sqref>
@@ -2816,7 +2819,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Wavelength Calibration'!$D$5:$D$16</c15:sqref>
@@ -2866,7 +2869,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{0000000D-FC21-41A1-8AD8-24EF512C9E61}"/>
                   </c:ext>
@@ -4979,14 +4982,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9C18372-B583-42F4-8F4E-BE2AF50AAC7B}" name="CalibData3" displayName="CalibData3" ref="L4:N26" totalsRowShown="0">
-  <autoFilter ref="L4:N26" xr:uid="{D9C18372-B583-42F4-8F4E-BE2AF50AAC7B}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D9C18372-B583-42F4-8F4E-BE2AF50AAC7B}" name="CalibData3" displayName="CalibData3" ref="L4:P25" totalsRowShown="0">
+  <autoFilter ref="L4:P25" xr:uid="{D9C18372-B583-42F4-8F4E-BE2AF50AAC7B}"/>
+  <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{10163724-6C7E-460B-BFF8-B4C78224821D}" name="Pixel Number (X)" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{90881FAE-4CA8-4278-A028-53B6A49AAC38}" name="Wavelength [nm] (Y)" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{78A89D84-58C0-415B-B8F1-DA850D4314FA}" name="Fitted Wavelength [nm]" dataDxfId="0">
       <calculatedColumnFormula>$P$5*L5^3 + $P$6*L5^2 + $P$7*L5 + $P$8</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="4" xr3:uid="{D45E345C-F212-4944-838D-31FF071230E9}" name="Column1"/>
+    <tableColumn id="5" xr3:uid="{1CB649FE-346F-42D3-8E7E-39F4C9C980CA}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5179,7 +5184,7 @@
     <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
     <col min="7" max="8" width="10" customWidth="1"/>
     <col min="12" max="12" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -5211,6 +5216,12 @@
       <c r="N4" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="O4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
@@ -5237,7 +5248,7 @@
         <v>650</v>
       </c>
       <c r="N5" s="5">
-        <f t="shared" ref="N5:N16" ca="1" si="1">$P$5*L5^3 + $P$6*L5^2 + $P$7*L5 + $P$8</f>
+        <f t="shared" ref="N5:N26" ca="1" si="1">$P$5*L5^3 + $P$6*L5^2 + $P$7*L5 + $P$8</f>
         <v>650.03276004180066</v>
       </c>
       <c r="O5" s="6" t="s">
@@ -5585,7 +5596,7 @@
         <v>900</v>
       </c>
       <c r="N16" s="5">
-        <f ca="1">$P$5*L16^3 + $P$6*L16^2 + $P$7*L16 + $P$8</f>
+        <f t="shared" ca="1" si="1"/>
         <v>901.99658378509093</v>
       </c>
     </row>
@@ -5596,8 +5607,8 @@
       <c r="M17" s="4">
         <v>680</v>
       </c>
-      <c r="N17" s="13">
-        <f ca="1">$P$5*L17^3 + $P$6*L17^2 + $P$7*L17 + $P$8</f>
+      <c r="N17" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>681.18290386702029</v>
       </c>
     </row>
@@ -5608,8 +5619,8 @@
       <c r="M18" s="4">
         <v>720</v>
       </c>
-      <c r="N18" s="13">
-        <f ca="1">$P$5*L18^3 + $P$6*L18^2 + $P$7*L18 + $P$8</f>
+      <c r="N18" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>720.3775475563009</v>
       </c>
     </row>
@@ -5620,20 +5631,20 @@
       <c r="M19" s="4">
         <v>740</v>
       </c>
-      <c r="N19" s="13">
-        <f ca="1">$P$5*L19^3 + $P$6*L19^2 + $P$7*L19 + $P$8</f>
+      <c r="N19" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>741.32732105236005</v>
       </c>
     </row>
     <row r="20" spans="12:14" x14ac:dyDescent="0.3">
-      <c r="L20" s="11">
+      <c r="L20" s="10">
         <v>2159</v>
       </c>
-      <c r="M20" s="11">
+      <c r="M20" s="10">
         <v>760</v>
       </c>
-      <c r="N20" s="14">
-        <f ca="1">$P$5*L20^3 + $P$6*L20^2 + $P$7*L20 + $P$8</f>
+      <c r="N20" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>759.91993858473984</v>
       </c>
     </row>
@@ -5644,8 +5655,8 @@
       <c r="M21" s="4">
         <v>785</v>
       </c>
-      <c r="N21" s="10">
-        <f ca="1">$P$5*L21^3 + $P$6*L21^2 + $P$7*L21 + $P$8</f>
+      <c r="N21" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>782.93140718226323</v>
       </c>
     </row>
@@ -5656,20 +5667,20 @@
       <c r="M22" s="4">
         <v>800</v>
       </c>
-      <c r="N22" s="10">
-        <f ca="1">$P$5*L22^3 + $P$6*L22^2 + $P$7*L22 + $P$8</f>
+      <c r="N22" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>799.43918663319619</v>
       </c>
     </row>
     <row r="23" spans="12:14" x14ac:dyDescent="0.3">
-      <c r="L23" s="11">
+      <c r="L23" s="10">
         <v>2358</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="10">
         <v>820</v>
       </c>
-      <c r="N23" s="12">
-        <f ca="1">$P$5*L23^3 + $P$6*L23^2 + $P$7*L23 + $P$8</f>
+      <c r="N23" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>818.57778583596132</v>
       </c>
     </row>
@@ -5680,8 +5691,8 @@
       <c r="M24" s="4">
         <v>840</v>
       </c>
-      <c r="N24" s="10">
-        <f ca="1">$P$5*L24^3 + $P$6*L24^2 + $P$7*L24 + $P$8</f>
+      <c r="N24" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>842.96831284636028</v>
       </c>
     </row>
@@ -5692,20 +5703,18 @@
       <c r="M25" s="4">
         <v>865</v>
       </c>
-      <c r="N25" s="10">
-        <f ca="1">$P$5*L25^3 + $P$6*L25^2 + $P$7*L25 + $P$8</f>
+      <c r="N25" s="11">
+        <f t="shared" ca="1" si="1"/>
         <v>861.43537367907629</v>
       </c>
     </row>
     <row r="26" spans="12:14" x14ac:dyDescent="0.3">
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12">
-        <f t="shared" ref="N24:N26" ca="1" si="2">$P$5*L26^3 + $P$6*L26^2 + $P$7*L26 + $P$8</f>
-        <v>173.17781565715251</v>
-      </c>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
